--- a/data/trans_orig/P1801_2016_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1801_2016_2023-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>126140</t>
+          <t>125933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161110</t>
+          <t>160449</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>136591</t>
+          <t>135759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>171549</t>
+          <t>171432</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>273541</t>
+          <t>271781</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>321061</t>
+          <t>321689</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132651</t>
+          <t>133312</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>167621</t>
+          <t>167828</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117154</t>
+          <t>117271</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152112</t>
+          <t>152944</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>261403</t>
+          <t>260775</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>308923</t>
+          <t>310683</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,34%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>212356</t>
+          <t>211005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>257498</t>
+          <t>257328</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>281455</t>
+          <t>280324</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>325094</t>
+          <t>325766</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>503152</t>
+          <t>503461</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>568077</t>
+          <t>568442</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>245077</t>
+          <t>245247</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>290219</t>
+          <t>291570</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>197990</t>
+          <t>197318</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>241629</t>
+          <t>242760</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>457582</t>
+          <t>457217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>522507</t>
+          <t>522198</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120756</t>
+          <t>119047</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153622</t>
+          <t>153754</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>168391</t>
+          <t>167284</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>205824</t>
+          <t>204179</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>297882</t>
+          <t>298601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>348427</t>
+          <t>350025</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,45%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164943</t>
+          <t>164811</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>197809</t>
+          <t>199518</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130485</t>
+          <t>132130</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167918</t>
+          <t>169025</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>306447</t>
+          <t>304849</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>356992</t>
+          <t>356273</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,4%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>186785</t>
+          <t>184701</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>224292</t>
+          <t>223727</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>216113</t>
+          <t>218296</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>256662</t>
+          <t>258429</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>417249</t>
+          <t>413245</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>471744</t>
+          <t>470939</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,19%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145672</t>
+          <t>146237</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183179</t>
+          <t>185263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130621</t>
+          <t>128854</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>171170</t>
+          <t>168987</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285503</t>
+          <t>286308</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>339998</t>
+          <t>344002</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,43%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82305</t>
+          <t>84554</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110792</t>
+          <t>110277</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105619</t>
+          <t>104028</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>134109</t>
+          <t>131570</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>193875</t>
+          <t>194792</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>236495</t>
+          <t>237891</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,35%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100429</t>
+          <t>100944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128916</t>
+          <t>126667</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84478</t>
+          <t>87017</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112968</t>
+          <t>114559</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>193313</t>
+          <t>191917</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>235933</t>
+          <t>235016</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,68%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>121637</t>
+          <t>122200</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>154613</t>
+          <t>154454</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>144943</t>
+          <t>146570</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>178892</t>
+          <t>178496</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>277921</t>
+          <t>278711</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>325877</t>
+          <t>322693</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,18%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>108510</t>
+          <t>108669</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>141486</t>
+          <t>140923</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>94223</t>
+          <t>94619</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128172</t>
+          <t>126545</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>210361</t>
+          <t>213545</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>258317</t>
+          <t>257527</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>207796</t>
+          <t>208241</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>258752</t>
+          <t>261642</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>312743</t>
+          <t>310390</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>366724</t>
+          <t>366737</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>533155</t>
+          <t>534251</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>612720</t>
+          <t>612544</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>397806</t>
+          <t>394916</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>448762</t>
+          <t>448317</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>324570</t>
+          <t>324557</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>378551</t>
+          <t>380904</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>735132</t>
+          <t>735308</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>814697</t>
+          <t>813601</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,36%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>361889</t>
+          <t>363639</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>421826</t>
+          <t>419305</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>489637</t>
+          <t>491106</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>548033</t>
+          <t>547851</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>871993</t>
+          <t>870208</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>955394</t>
+          <t>952287</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,34%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>356757</t>
+          <t>359278</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>416694</t>
+          <t>414944</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>278134</t>
+          <t>278316</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>336530</t>
+          <t>335061</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>649356</t>
+          <t>652463</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>732757</t>
+          <t>734542</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1517483</t>
+          <t>1524395</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1638137</t>
+          <t>1638978</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1966592</t>
+          <t>1962823</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2083332</t>
+          <t>2088270</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3512610</t>
+          <t>3525518</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3685006</t>
+          <t>3700078</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1756213</t>
+          <t>1755372</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1876867</t>
+          <t>1869955</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1461210</t>
+          <t>1456272</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1577950</t>
+          <t>1581719</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3253886</t>
+          <t>3238814</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3426282</t>
+          <t>3413374</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -4049,32 +4049,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>207212</t>
+          <t>202002</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>185608</t>
+          <t>184206</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>226193</t>
+          <t>219048</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4084,17 +4084,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>206071</t>
+          <t>224879</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190625</t>
+          <t>211497</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>219933</t>
+          <t>237723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4119,32 +4119,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>413283</t>
+          <t>426881</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>382937</t>
+          <t>402115</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>436498</t>
+          <t>449204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -4162,32 +4162,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>102949</t>
+          <t>115765</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83968</t>
+          <t>98719</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>124553</t>
+          <t>133561</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4197,17 +4197,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>83564</t>
+          <t>91182</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69702</t>
+          <t>78338</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99010</t>
+          <t>104564</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4232,32 +4232,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>186513</t>
+          <t>206947</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>163298</t>
+          <t>184624</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>216859</t>
+          <t>231713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -4275,17 +4275,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>310161</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>310161</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>310161</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4345,17 +4345,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>633828</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>633828</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>599796</t>
+          <t>633828</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>128201</t>
+          <t>133126</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>105445</t>
+          <t>110945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>152563</t>
+          <t>158813</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>155278</t>
+          <t>160942</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>138751</t>
+          <t>142901</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>175762</t>
+          <t>180832</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4462,32 +4462,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>283478</t>
+          <t>294068</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>253952</t>
+          <t>265074</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>313127</t>
+          <t>325197</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -4505,32 +4505,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>390189</t>
+          <t>397521</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365827</t>
+          <t>371834</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>412945</t>
+          <t>419702</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>357931</t>
+          <t>383733</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337447</t>
+          <t>363843</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374458</t>
+          <t>401774</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4575,32 +4575,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>748120</t>
+          <t>781254</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>718471</t>
+          <t>750125</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>777646</t>
+          <t>810248</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,35%</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4618,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513209</t>
+          <t>544675</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513209</t>
+          <t>544675</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513209</t>
+          <t>544675</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4688,17 +4688,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031598</t>
+          <t>1075322</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031598</t>
+          <t>1075322</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031598</t>
+          <t>1075322</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>205440</t>
+          <t>205376</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>187441</t>
+          <t>187825</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>221250</t>
+          <t>223314</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>241186</t>
+          <t>242802</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>225726</t>
+          <t>228018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>256199</t>
+          <t>258185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4805,32 +4805,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>446627</t>
+          <t>448178</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>422479</t>
+          <t>425546</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>468854</t>
+          <t>470840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,12%</t>
         </is>
       </c>
     </row>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>110610</t>
+          <t>110617</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94800</t>
+          <t>92679</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128609</t>
+          <t>128168</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>107020</t>
+          <t>112691</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92007</t>
+          <t>97308</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122480</t>
+          <t>127475</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>217629</t>
+          <t>223308</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>195402</t>
+          <t>200646</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>241777</t>
+          <t>245940</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -4961,17 +4961,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>348206</t>
+          <t>355493</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>348206</t>
+          <t>355493</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>348206</t>
+          <t>355493</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5031,17 +5031,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664256</t>
+          <t>671486</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664256</t>
+          <t>671486</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664256</t>
+          <t>671486</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>161350</t>
+          <t>185603</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>136922</t>
+          <t>159919</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>183356</t>
+          <t>211006</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>200879</t>
+          <t>225628</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127384</t>
+          <t>205741</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>251211</t>
+          <t>246423</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5148,32 +5148,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>362229</t>
+          <t>411231</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>251428</t>
+          <t>377803</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>421170</t>
+          <t>441327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>55,58%</t>
         </is>
       </c>
     </row>
@@ -5191,32 +5191,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>151207</t>
+          <t>187542</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129201</t>
+          <t>162139</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>175635</t>
+          <t>213226</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>273801</t>
+          <t>195270</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223469</t>
+          <t>174475</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>347296</t>
+          <t>215157</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>425008</t>
+          <t>382812</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>366067</t>
+          <t>352716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>535809</t>
+          <t>416240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>52,42%</t>
         </is>
       </c>
     </row>
@@ -5304,17 +5304,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5339,17 +5339,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>474680</t>
+          <t>420898</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>474680</t>
+          <t>420898</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>474680</t>
+          <t>420898</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5374,17 +5374,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787237</t>
+          <t>794043</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787237</t>
+          <t>794043</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787237</t>
+          <t>794043</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5421,32 +5421,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>106197</t>
+          <t>115255</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94033</t>
+          <t>103061</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119004</t>
+          <t>127314</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5456,32 +5456,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>142384</t>
+          <t>151552</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131609</t>
+          <t>140267</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151265</t>
+          <t>162531</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5491,32 +5491,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>248581</t>
+          <t>266807</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>232364</t>
+          <t>249028</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>264357</t>
+          <t>282826</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>65,34%</t>
         </is>
       </c>
     </row>
@@ -5534,32 +5534,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>72545</t>
+          <t>90410</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59738</t>
+          <t>78351</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84709</t>
+          <t>102604</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66272</t>
+          <t>75663</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57391</t>
+          <t>64684</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77047</t>
+          <t>86948</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5604,32 +5604,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>138817</t>
+          <t>166072</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123041</t>
+          <t>150053</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>155034</t>
+          <t>183851</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -5647,17 +5647,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5717,17 +5717,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5764,32 +5764,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>164224</t>
+          <t>162308</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>148896</t>
+          <t>147697</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>178901</t>
+          <t>176673</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5799,32 +5799,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>177547</t>
+          <t>180894</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>163789</t>
+          <t>168253</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>189115</t>
+          <t>193419</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5834,32 +5834,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>341772</t>
+          <t>343202</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>318794</t>
+          <t>323274</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>360400</t>
+          <t>363742</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -5877,32 +5877,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>105412</t>
+          <t>108399</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90735</t>
+          <t>94034</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>120740</t>
+          <t>123010</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5912,32 +5912,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>78828</t>
+          <t>82194</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67260</t>
+          <t>69669</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>92586</t>
+          <t>94835</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5947,32 +5947,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>184239</t>
+          <t>190593</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>165611</t>
+          <t>170053</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>207217</t>
+          <t>210521</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -5990,17 +5990,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6025,17 +6025,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256375</t>
+          <t>263088</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256375</t>
+          <t>263088</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256375</t>
+          <t>263088</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526011</t>
+          <t>533795</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526011</t>
+          <t>533795</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526011</t>
+          <t>533795</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6107,32 +6107,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>379721</t>
+          <t>427117</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>346114</t>
+          <t>395967</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>407183</t>
+          <t>456892</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6142,32 +6142,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>654905</t>
+          <t>543735</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>584367</t>
+          <t>519074</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>751457</t>
+          <t>567914</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6177,32 +6177,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1034626</t>
+          <t>970852</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>951061</t>
+          <t>930284</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1215038</t>
+          <t>1009825</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -6220,32 +6220,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>242524</t>
+          <t>290372</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>215062</t>
+          <t>260597</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>276131</t>
+          <t>321522</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6255,32 +6255,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>192908</t>
+          <t>225273</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>96356</t>
+          <t>201094</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>263446</t>
+          <t>249934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6290,32 +6290,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>435433</t>
+          <t>515645</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>255021</t>
+          <t>476672</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>518998</t>
+          <t>556213</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -6333,17 +6333,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>622245</t>
+          <t>717489</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>622245</t>
+          <t>717489</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>622245</t>
+          <t>717489</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>847813</t>
+          <t>769008</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>847813</t>
+          <t>769008</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>847813</t>
+          <t>769008</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6403,17 +6403,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1470059</t>
+          <t>1486497</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1470059</t>
+          <t>1486497</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1470059</t>
+          <t>1486497</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6450,32 +6450,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>474478</t>
+          <t>260871</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>301193</t>
+          <t>234838</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>712285</t>
+          <t>288667</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6485,32 +6485,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>310003</t>
+          <t>354134</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>287251</t>
+          <t>328904</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>331759</t>
+          <t>378652</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6520,32 +6520,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>784481</t>
+          <t>615006</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>622312</t>
+          <t>579770</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1103437</t>
+          <t>653779</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -6563,32 +6563,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>454242</t>
+          <t>537201</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>216435</t>
+          <t>509405</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>627527</t>
+          <t>563234</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6598,32 +6598,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>407728</t>
+          <t>477197</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>385972</t>
+          <t>452679</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>430480</t>
+          <t>502427</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6633,32 +6633,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>861971</t>
+          <t>1014397</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>543015</t>
+          <t>975624</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1024140</t>
+          <t>1049633</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>64,42%</t>
         </is>
       </c>
     </row>
@@ -6676,17 +6676,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6711,17 +6711,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6746,17 +6746,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1826823</t>
+          <t>1691660</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1682575</t>
+          <t>1626326</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2227435</t>
+          <t>1757140</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2088253</t>
+          <t>2084564</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1952295</t>
+          <t>2026244</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2367460</t>
+          <t>2136118</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6863,32 +6863,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3915075</t>
+          <t>3776224</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3688333</t>
+          <t>3695188</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4351924</t>
+          <t>3868475</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>53,3%</t>
         </is>
       </c>
     </row>
@@ -6906,32 +6906,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1629678</t>
+          <t>1837826</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1229066</t>
+          <t>1772346</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1773926</t>
+          <t>1903160</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1568052</t>
+          <t>1643204</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1288845</t>
+          <t>1591650</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1704010</t>
+          <t>1701524</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6976,32 +6976,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3197731</t>
+          <t>3481030</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2760882</t>
+          <t>3388779</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3424473</t>
+          <t>3562066</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -7019,17 +7019,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3456501</t>
+          <t>3529486</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3456501</t>
+          <t>3529486</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3456501</t>
+          <t>3529486</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7054,17 +7054,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3656305</t>
+          <t>3727768</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3656305</t>
+          <t>3727768</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3656305</t>
+          <t>3727768</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7089,17 +7089,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7112806</t>
+          <t>7257254</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7112806</t>
+          <t>7257254</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7112806</t>
+          <t>7257254</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
